--- a/resources/templates/standard/A5100-02.xlsx
+++ b/resources/templates/standard/A5100-02.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="111">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t xml:space="preserve">내부심사 실시 계획서 (갑지)
 (품질&amp;환경&amp;안전 시스템)</t>
@@ -1047,12 +1050,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1071,20 +1076,20 @@
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
       <c r="V1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA1" s="4"/>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD1" s="4"/>
       <c r="AE1" s="4"/>
@@ -1259,7 +1264,7 @@
     </row>
     <row r="4" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1271,13 +1276,13 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
@@ -1285,7 +1290,7 @@
       <c r="S4" s="8"/>
       <c r="T4" s="8"/>
       <c r="U4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1334,7 +1339,7 @@
     </row>
     <row r="5" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1403,7 +1408,7 @@
     </row>
     <row r="6" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1472,7 +1477,7 @@
     </row>
     <row r="7" ht="21.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
@@ -1489,7 +1494,7 @@
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
       <c r="P7" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q7" s="13"/>
       <c r="R7" s="13"/>
@@ -1543,52 +1548,52 @@
     </row>
     <row r="8" ht="39.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="14"/>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
       <c r="E8" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="15"/>
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
       <c r="Q8" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
       <c r="T8" s="16"/>
       <c r="U8" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V8" s="16"/>
       <c r="W8" s="16"/>
       <c r="X8" s="16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB8" s="16"/>
       <c r="AC8" s="16"/>
       <c r="AD8" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8" s="15"/>
       <c r="AF8" s="5"/>
@@ -1596,41 +1601,41 @@
       <c r="AH8" s="5"/>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK8" s="17"/>
       <c r="AL8" s="17"/>
       <c r="AM8" s="17"/>
       <c r="AN8" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO8" s="17"/>
       <c r="AP8" s="17"/>
       <c r="AQ8" s="17"/>
       <c r="AR8" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS8" s="17"/>
       <c r="AT8" s="17"/>
       <c r="AU8" s="17"/>
       <c r="AV8" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW8" s="17"/>
       <c r="AX8" s="17"/>
       <c r="AY8" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ8" s="17"/>
       <c r="BA8" s="17"/>
       <c r="BB8" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC8" s="17"/>
       <c r="BD8" s="17"/>
       <c r="BE8" s="5"/>
       <c r="BF8" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG8" s="18"/>
       <c r="BH8" s="18"/>
@@ -1642,7 +1647,7 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -2558,11 +2563,11 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="8"/>
@@ -2765,7 +2770,7 @@
       <c r="A23" s="31"/>
       <c r="B23" s="31"/>
       <c r="C23" s="32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23" s="32"/>
       <c r="E23" s="6"/>
@@ -2901,7 +2906,7 @@
       <c r="A25" s="31"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D25" s="32"/>
       <c r="E25" s="6"/>
@@ -3035,19 +3040,19 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
       <c r="H27" s="21"/>
       <c r="I27" s="21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
@@ -3061,21 +3066,21 @@
       <c r="S27" s="21"/>
       <c r="T27" s="21"/>
       <c r="U27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AA27" s="4"/>
       <c r="AB27" s="4"/>
       <c r="AC27" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AD27" s="4"/>
       <c r="AE27" s="4"/>
@@ -3138,17 +3143,17 @@
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="X28" s="6"/>
       <c r="Y28" s="6"/>
       <c r="Z28" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AA28" s="6"/>
       <c r="AB28" s="6"/>
       <c r="AC28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AD28" s="6"/>
       <c r="AE28" s="6"/>
@@ -3211,17 +3216,17 @@
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X29" s="12"/>
       <c r="Y29" s="12"/>
       <c r="Z29" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AA29" s="12"/>
       <c r="AB29" s="12"/>
       <c r="AC29" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AD29" s="12"/>
       <c r="AE29" s="12"/>
@@ -3266,7 +3271,7 @@
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -3465,7 +3470,7 @@
     </row>
     <row r="33" ht="18" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -3480,7 +3485,7 @@
       <c r="I33" s="8"/>
       <c r="J33" s="8"/>
       <c r="K33" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -3495,7 +3500,7 @@
       <c r="S33" s="8"/>
       <c r="T33" s="8"/>
       <c r="U33" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
@@ -3547,7 +3552,7 @@
     </row>
     <row r="34" ht="18" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -3619,7 +3624,7 @@
     </row>
     <row r="35" ht="18" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -3691,7 +3696,7 @@
     </row>
     <row r="36" ht="18" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3711,7 +3716,7 @@
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
       <c r="P36" s="13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -3768,18 +3773,18 @@
     </row>
     <row r="37" ht="18" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
       <c r="D37" s="19"/>
       <c r="E37" s="19"/>
       <c r="F37" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" s="4"/>
       <c r="H37" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -3787,7 +3792,7 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
@@ -3795,7 +3800,7 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
@@ -3803,7 +3808,7 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA37" s="4"/>
       <c r="AB37" s="4"/>
@@ -3852,11 +3857,11 @@
       <c r="D38" s="19"/>
       <c r="E38" s="19"/>
       <c r="F38" s="32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G38" s="32"/>
       <c r="H38" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
@@ -3864,7 +3869,7 @@
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
       <c r="N38" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
@@ -3872,7 +3877,7 @@
       <c r="R38" s="6"/>
       <c r="S38" s="6"/>
       <c r="T38" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U38" s="6"/>
       <c r="V38" s="6"/>
@@ -3880,7 +3885,7 @@
       <c r="X38" s="6"/>
       <c r="Y38" s="6"/>
       <c r="Z38" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA38" s="6"/>
       <c r="AB38" s="6"/>
@@ -3929,11 +3934,11 @@
       <c r="D39" s="19"/>
       <c r="E39" s="19"/>
       <c r="F39" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G39" s="32"/>
       <c r="H39" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I39" s="6"/>
       <c r="J39" s="6"/>
@@ -3941,7 +3946,7 @@
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
@@ -3949,7 +3954,7 @@
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U39" s="6"/>
       <c r="V39" s="6"/>
@@ -3957,7 +3962,7 @@
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
       <c r="Z39" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA39" s="6"/>
       <c r="AB39" s="6"/>
@@ -4001,18 +4006,18 @@
     </row>
     <row r="40" ht="27.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" s="33"/>
       <c r="C40" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D40" s="32"/>
       <c r="E40" s="32"/>
       <c r="F40" s="32"/>
       <c r="G40" s="32"/>
       <c r="H40" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
@@ -4076,14 +4081,14 @@
       <c r="A41" s="33"/>
       <c r="B41" s="33"/>
       <c r="C41" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D41" s="32"/>
       <c r="E41" s="32"/>
       <c r="F41" s="32"/>
       <c r="G41" s="32"/>
       <c r="H41" s="35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I41" s="35"/>
       <c r="J41" s="35"/>
@@ -4091,7 +4096,7 @@
       <c r="L41" s="35"/>
       <c r="M41" s="35"/>
       <c r="N41" s="35" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="O41" s="35"/>
       <c r="P41" s="35"/>
@@ -4099,7 +4104,7 @@
       <c r="R41" s="35"/>
       <c r="S41" s="35"/>
       <c r="T41" s="35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U41" s="35"/>
       <c r="V41" s="35"/>
@@ -4107,7 +4112,7 @@
       <c r="X41" s="35"/>
       <c r="Y41" s="35"/>
       <c r="Z41" s="35" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AA41" s="35"/>
       <c r="AB41" s="35"/>
@@ -4153,14 +4158,14 @@
       <c r="A42" s="33"/>
       <c r="B42" s="33"/>
       <c r="C42" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D42" s="32"/>
       <c r="E42" s="32"/>
       <c r="F42" s="32"/>
       <c r="G42" s="32"/>
       <c r="H42" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I42" s="35"/>
       <c r="J42" s="35"/>
@@ -4168,7 +4173,7 @@
       <c r="L42" s="35"/>
       <c r="M42" s="35"/>
       <c r="N42" s="35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O42" s="35"/>
       <c r="P42" s="35"/>
@@ -4176,7 +4181,7 @@
       <c r="R42" s="35"/>
       <c r="S42" s="35"/>
       <c r="T42" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="U42" s="35"/>
       <c r="V42" s="35"/>
@@ -4228,14 +4233,14 @@
       <c r="A43" s="33"/>
       <c r="B43" s="33"/>
       <c r="C43" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D43" s="32"/>
       <c r="E43" s="32"/>
       <c r="F43" s="32"/>
       <c r="G43" s="32"/>
       <c r="H43" s="35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I43" s="35"/>
       <c r="J43" s="35"/>
@@ -4243,7 +4248,7 @@
       <c r="L43" s="35"/>
       <c r="M43" s="35"/>
       <c r="N43" s="35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O43" s="35"/>
       <c r="P43" s="35"/>
@@ -4257,7 +4262,7 @@
       <c r="X43" s="35"/>
       <c r="Y43" s="35"/>
       <c r="Z43" s="35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA43" s="35"/>
       <c r="AB43" s="35"/>
@@ -4303,14 +4308,14 @@
       <c r="A44" s="33"/>
       <c r="B44" s="33"/>
       <c r="C44" s="32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D44" s="32"/>
       <c r="E44" s="32"/>
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
       <c r="H44" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
@@ -4374,14 +4379,14 @@
       <c r="A45" s="33"/>
       <c r="B45" s="33"/>
       <c r="C45" s="32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D45" s="32"/>
       <c r="E45" s="32"/>
       <c r="F45" s="32"/>
       <c r="G45" s="32"/>
       <c r="H45" s="35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I45" s="35"/>
       <c r="J45" s="35"/>
@@ -4389,7 +4394,7 @@
       <c r="L45" s="35"/>
       <c r="M45" s="35"/>
       <c r="N45" s="35" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O45" s="35"/>
       <c r="P45" s="35"/>
@@ -4397,7 +4402,7 @@
       <c r="R45" s="35"/>
       <c r="S45" s="35"/>
       <c r="T45" s="35" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U45" s="35"/>
       <c r="V45" s="35"/>
@@ -4405,7 +4410,7 @@
       <c r="X45" s="35"/>
       <c r="Y45" s="35"/>
       <c r="Z45" s="35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AA45" s="35"/>
       <c r="AB45" s="35"/>
@@ -4451,14 +4456,14 @@
       <c r="A46" s="33"/>
       <c r="B46" s="33"/>
       <c r="C46" s="32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D46" s="32"/>
       <c r="E46" s="32"/>
       <c r="F46" s="32"/>
       <c r="G46" s="32"/>
       <c r="H46" s="35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I46" s="35"/>
       <c r="J46" s="35"/>
@@ -4466,7 +4471,7 @@
       <c r="L46" s="35"/>
       <c r="M46" s="35"/>
       <c r="N46" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O46" s="35"/>
       <c r="P46" s="35"/>
@@ -4474,7 +4479,7 @@
       <c r="R46" s="35"/>
       <c r="S46" s="35"/>
       <c r="T46" s="39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U46" s="39"/>
       <c r="V46" s="39"/>
@@ -4482,7 +4487,7 @@
       <c r="X46" s="39"/>
       <c r="Y46" s="39"/>
       <c r="Z46" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AA46" s="35"/>
       <c r="AB46" s="35"/>
@@ -4528,14 +4533,14 @@
       <c r="A47" s="33"/>
       <c r="B47" s="33"/>
       <c r="C47" s="32" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D47" s="32"/>
       <c r="E47" s="32"/>
       <c r="F47" s="32"/>
       <c r="G47" s="32"/>
       <c r="H47" s="35" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I47" s="35"/>
       <c r="J47" s="35"/>
@@ -4543,7 +4548,7 @@
       <c r="L47" s="35"/>
       <c r="M47" s="35"/>
       <c r="N47" s="35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O47" s="35"/>
       <c r="P47" s="35"/>
@@ -4551,7 +4556,7 @@
       <c r="R47" s="35"/>
       <c r="S47" s="35"/>
       <c r="T47" s="39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U47" s="39"/>
       <c r="V47" s="39"/>
@@ -4603,14 +4608,14 @@
       <c r="A48" s="33"/>
       <c r="B48" s="33"/>
       <c r="C48" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D48" s="32"/>
       <c r="E48" s="32"/>
       <c r="F48" s="32"/>
       <c r="G48" s="32"/>
       <c r="H48" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I48" s="35"/>
       <c r="J48" s="35"/>
@@ -4618,7 +4623,7 @@
       <c r="L48" s="35"/>
       <c r="M48" s="35"/>
       <c r="N48" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O48" s="35"/>
       <c r="P48" s="35"/>
@@ -4626,7 +4631,7 @@
       <c r="R48" s="35"/>
       <c r="S48" s="35"/>
       <c r="T48" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U48" s="40"/>
       <c r="V48" s="40"/>
@@ -4634,7 +4639,7 @@
       <c r="X48" s="40"/>
       <c r="Y48" s="40"/>
       <c r="Z48" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA48" s="35"/>
       <c r="AB48" s="35"/>
@@ -4680,14 +4685,14 @@
       <c r="A49" s="33"/>
       <c r="B49" s="33"/>
       <c r="C49" s="32" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D49" s="32"/>
       <c r="E49" s="32"/>
       <c r="F49" s="32"/>
       <c r="G49" s="32"/>
       <c r="H49" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I49" s="6"/>
       <c r="J49" s="6"/>
@@ -4751,14 +4756,14 @@
       <c r="A50" s="33"/>
       <c r="B50" s="33"/>
       <c r="C50" s="32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D50" s="32"/>
       <c r="E50" s="32"/>
       <c r="F50" s="32"/>
       <c r="G50" s="32"/>
       <c r="H50" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I50" s="35"/>
       <c r="J50" s="35"/>
@@ -4766,7 +4771,7 @@
       <c r="L50" s="35"/>
       <c r="M50" s="35"/>
       <c r="N50" s="40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O50" s="40"/>
       <c r="P50" s="40"/>
@@ -4774,7 +4779,7 @@
       <c r="R50" s="40"/>
       <c r="S50" s="40"/>
       <c r="T50" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U50" s="40"/>
       <c r="V50" s="40"/>
@@ -4782,7 +4787,7 @@
       <c r="X50" s="40"/>
       <c r="Y50" s="40"/>
       <c r="Z50" s="35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AA50" s="35"/>
       <c r="AB50" s="35"/>
@@ -4828,14 +4833,14 @@
       <c r="A51" s="33"/>
       <c r="B51" s="33"/>
       <c r="C51" s="32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D51" s="32"/>
       <c r="E51" s="32"/>
       <c r="F51" s="32"/>
       <c r="G51" s="32"/>
       <c r="H51" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I51" s="22"/>
       <c r="J51" s="22"/>
@@ -4849,7 +4854,7 @@
       <c r="R51" s="40"/>
       <c r="S51" s="40"/>
       <c r="T51" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U51" s="22"/>
       <c r="V51" s="22"/>
@@ -4857,7 +4862,7 @@
       <c r="X51" s="22"/>
       <c r="Y51" s="22"/>
       <c r="Z51" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA51" s="22"/>
       <c r="AB51" s="22"/>
@@ -4901,18 +4906,18 @@
     </row>
     <row r="52" ht="27.95" customHeight="1" spans="1:65" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B52" s="33"/>
       <c r="C52" s="32" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D52" s="32"/>
       <c r="E52" s="32"/>
       <c r="F52" s="32"/>
       <c r="G52" s="32"/>
       <c r="H52" s="40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I52" s="40"/>
       <c r="J52" s="40"/>
@@ -4920,7 +4925,7 @@
       <c r="L52" s="40"/>
       <c r="M52" s="40"/>
       <c r="N52" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O52" s="40"/>
       <c r="P52" s="40"/>
@@ -4928,7 +4933,7 @@
       <c r="R52" s="40"/>
       <c r="S52" s="40"/>
       <c r="T52" s="40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U52" s="40"/>
       <c r="V52" s="40"/>
@@ -4936,7 +4941,7 @@
       <c r="X52" s="40"/>
       <c r="Y52" s="40"/>
       <c r="Z52" s="40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AA52" s="40"/>
       <c r="AB52" s="40"/>
@@ -4982,7 +4987,7 @@
       <c r="A53" s="33"/>
       <c r="B53" s="33"/>
       <c r="C53" s="32" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D53" s="32"/>
       <c r="E53" s="32"/>
@@ -5051,14 +5056,14 @@
       <c r="A54" s="33"/>
       <c r="B54" s="33"/>
       <c r="C54" s="32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D54" s="32"/>
       <c r="E54" s="32"/>
       <c r="F54" s="32"/>
       <c r="G54" s="32"/>
       <c r="H54" s="41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I54" s="41"/>
       <c r="J54" s="41"/>
@@ -5066,7 +5071,7 @@
       <c r="L54" s="41"/>
       <c r="M54" s="41"/>
       <c r="N54" s="41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O54" s="41"/>
       <c r="P54" s="41"/>
@@ -5074,7 +5079,7 @@
       <c r="R54" s="41"/>
       <c r="S54" s="41"/>
       <c r="T54" s="41" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U54" s="41"/>
       <c r="V54" s="41"/>
@@ -5082,7 +5087,7 @@
       <c r="X54" s="41"/>
       <c r="Y54" s="41"/>
       <c r="Z54" s="41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA54" s="41"/>
       <c r="AB54" s="41"/>
@@ -5128,14 +5133,14 @@
       <c r="A55" s="33"/>
       <c r="B55" s="33"/>
       <c r="C55" s="32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D55" s="32"/>
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
       <c r="G55" s="32"/>
       <c r="H55" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I55" s="22"/>
       <c r="J55" s="22"/>
@@ -5143,7 +5148,7 @@
       <c r="L55" s="22"/>
       <c r="M55" s="22"/>
       <c r="N55" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O55" s="22"/>
       <c r="P55" s="22"/>
@@ -5151,7 +5156,7 @@
       <c r="R55" s="22"/>
       <c r="S55" s="22"/>
       <c r="T55" s="41" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U55" s="41"/>
       <c r="V55" s="41"/>
@@ -5159,7 +5164,7 @@
       <c r="X55" s="41"/>
       <c r="Y55" s="41"/>
       <c r="Z55" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA55" s="22"/>
       <c r="AB55" s="22"/>
@@ -5205,14 +5210,14 @@
       <c r="A56" s="33"/>
       <c r="B56" s="33"/>
       <c r="C56" s="32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D56" s="32"/>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
       <c r="G56" s="32"/>
       <c r="H56" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
@@ -5276,14 +5281,14 @@
       <c r="A57" s="33"/>
       <c r="B57" s="33"/>
       <c r="C57" s="42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57" s="42"/>
       <c r="E57" s="42"/>
       <c r="F57" s="42"/>
       <c r="G57" s="42"/>
       <c r="H57" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
